--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>132159497</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>132159497</v>
       </c>
       <c r="B3" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>132159497</v>
       </c>
       <c r="B3" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>132159497</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59178-2022 artfynd.xlsx
+++ b/artfynd/A 59178-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106104302</v>
+        <v>105993947</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hultebo äng, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594027.1003345472</v>
+        <v>593968</v>
       </c>
       <c r="R2" t="n">
-        <v>6395498.475115538</v>
+        <v>6395505</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132159497</v>
+        <v>106104302</v>
       </c>
       <c r="B3" t="n">
-        <v>58115</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,39 +793,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Sm</t>
+          <t>Hultebo äng, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594207</v>
+        <v>594028</v>
       </c>
       <c r="R3" t="n">
-        <v>6395283</v>
+        <v>6395499</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -858,22 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2023-01-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2023-01-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,50 +890,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133689188</v>
+        <v>118330379</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Sm</t>
+          <t>Fridhem, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594256</v>
+        <v>594163</v>
       </c>
       <c r="R4" t="n">
-        <v>6395258</v>
+        <v>6395320</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,22 +960,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1127,6 +1117,462 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106104873</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hultebo äng, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594050</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6395495</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-01-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-01-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106105651</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594163</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6395320</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-01-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-01-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132159497</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594207</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6395283</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133689188</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594256</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6395258</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västrum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
